--- a/exports/trend_1d/IDEA_full_report.xlsx
+++ b/exports/trend_1d/IDEA_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q79"/>
+  <dimension ref="A1:U79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>9.01</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42044</v>
+        <v>42045</v>
       </c>
       <c r="H2" t="n">
-        <v>92.95</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="I2" t="n">
         <v>92.32718440685001</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K2" t="n">
-        <v>2.54</v>
+        <v>0.5</v>
       </c>
       <c r="L2" t="n">
         <v>1.16</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,28 +626,28 @@
         <v>10.75</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42073</v>
+        <v>42074</v>
       </c>
       <c r="H3" t="n">
-        <v>92.95</v>
+        <v>99</v>
       </c>
       <c r="I3" t="n">
         <v>98.46881099026761</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K3" t="n">
-        <v>-2.03</v>
+        <v>-8.67</v>
       </c>
       <c r="L3" t="n">
-        <v>7.79</v>
+        <v>9.82</v>
       </c>
       <c r="M3" t="n">
         <v>2.19</v>
       </c>
       <c r="N3" t="n">
-        <v>3.28</v>
+        <v>6.51</v>
       </c>
       <c r="O3" t="n">
         <v>-1.99</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42061</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>15.75</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42123</v>
+        <v>42124</v>
       </c>
       <c r="H4" t="n">
-        <v>109.65</v>
+        <v>105.7</v>
       </c>
       <c r="I4" t="n">
         <v>106.6774546930669</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K4" t="n">
-        <v>10.76</v>
+        <v>6.77</v>
       </c>
       <c r="L4" t="n">
         <v>6.46</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42089</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>16.56</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42282</v>
+        <v>42283</v>
       </c>
       <c r="H5" t="n">
-        <v>92.90000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="I5" t="n">
         <v>93.08694747366887</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="K5" t="n">
-        <v>12.11</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="L5" t="n">
         <v>6.58</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>109</v>
+        <v>110</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42152</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>6</v>
+      </c>
+      <c r="U5" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -762,28 +833,28 @@
         <v>11.99</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42298</v>
+        <v>42300</v>
       </c>
       <c r="H6" t="n">
-        <v>91.75</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="I6" t="n">
         <v>86.385715703543</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K6" t="n">
-        <v>-4.23</v>
+        <v>-11.43</v>
       </c>
       <c r="L6" t="n">
-        <v>6.99</v>
+        <v>13</v>
       </c>
       <c r="M6" t="n">
-        <v>1.3</v>
+        <v>2.13</v>
       </c>
       <c r="N6" t="n">
-        <v>3.3</v>
+        <v>7.52</v>
       </c>
       <c r="O6" t="n">
         <v>3.12</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42306</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>14.15</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42332</v>
+        <v>42334</v>
       </c>
       <c r="H7" t="n">
-        <v>84.7</v>
+        <v>88.7</v>
       </c>
       <c r="I7" t="n">
         <v>86.17690780067365</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K7" t="n">
-        <v>0.18</v>
+        <v>-4.54</v>
       </c>
       <c r="L7" t="n">
         <v>6.95</v>
@@ -840,7 +923,7 @@
         <v>1.53</v>
       </c>
       <c r="N7" t="n">
-        <v>3.03</v>
+        <v>4.72</v>
       </c>
       <c r="O7" t="n">
         <v>-7.52</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42306</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>13.56</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42377</v>
+        <v>42380</v>
       </c>
       <c r="H8" t="n">
-        <v>80.40000000000001</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="I8" t="n">
         <v>80.27098499295317</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K8" t="n">
-        <v>-9.359999999999999</v>
+        <v>-11.61</v>
       </c>
       <c r="L8" t="n">
         <v>12.06</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42369</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>9.720000000000001</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42459</v>
+        <v>42460</v>
       </c>
       <c r="H9" t="n">
-        <v>65.95</v>
+        <v>66.55</v>
       </c>
       <c r="I9" t="n">
         <v>66.10146010583171</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K9" t="n">
-        <v>15.88</v>
+        <v>15.11</v>
       </c>
       <c r="L9" t="n">
         <v>2.1</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>8.73</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42494</v>
+        <v>42495</v>
       </c>
       <c r="H10" t="n">
-        <v>72.40000000000001</v>
+        <v>68.55</v>
       </c>
       <c r="I10" t="n">
         <v>68.92533768497412</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K10" t="n">
-        <v>8.789999999999999</v>
+        <v>3.01</v>
       </c>
       <c r="L10" t="n">
         <v>3.46</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42488</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>15.89</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42564</v>
+        <v>42565</v>
       </c>
       <c r="H11" t="n">
-        <v>64.40000000000001</v>
+        <v>65</v>
       </c>
       <c r="I11" t="n">
         <v>64.83165752009077</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K11" t="n">
-        <v>6.05</v>
+        <v>5.18</v>
       </c>
       <c r="L11" t="n">
         <v>7.29</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42516</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1104,25 +1247,25 @@
         <v>7.75</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42590</v>
+        <v>42591</v>
       </c>
       <c r="H12" t="n">
-        <v>62.25</v>
+        <v>58.7</v>
       </c>
       <c r="I12" t="n">
         <v>61.32549532728012</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K12" t="n">
-        <v>-4.23</v>
+        <v>-9.69</v>
       </c>
       <c r="L12" t="n">
-        <v>4.92</v>
+        <v>10.08</v>
       </c>
       <c r="M12" t="n">
-        <v>0.24</v>
+        <v>4.9</v>
       </c>
       <c r="N12" t="n">
         <v>6.48</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42579</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,25 +1316,25 @@
         <v>10.82</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42702</v>
+        <v>42703</v>
       </c>
       <c r="H13" t="n">
-        <v>45.8</v>
+        <v>47.85</v>
       </c>
       <c r="I13" t="n">
         <v>47.50462287230392</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K13" t="n">
-        <v>21.98</v>
+        <v>18.48</v>
       </c>
       <c r="L13" t="n">
         <v>4.94</v>
       </c>
       <c r="M13" t="n">
-        <v>2.41</v>
+        <v>3.28</v>
       </c>
       <c r="N13" t="n">
         <v>6.83</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42607</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>5</v>
+      </c>
+      <c r="U13" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -1218,22 +1385,22 @@
         <v>11.13</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42727</v>
+        <v>42730</v>
       </c>
       <c r="H14" t="n">
-        <v>42.75</v>
+        <v>41.9</v>
       </c>
       <c r="I14" t="n">
         <v>42.52366874693374</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K14" t="n">
-        <v>-10.66</v>
+        <v>-12.43</v>
       </c>
       <c r="L14" t="n">
-        <v>10.97</v>
+        <v>12.75</v>
       </c>
       <c r="M14" t="n">
         <v>2.39</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42733</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,28 +1454,28 @@
         <v>11.12</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42758</v>
+        <v>42759</v>
       </c>
       <c r="H15" t="n">
-        <v>44.3</v>
+        <v>45.85</v>
       </c>
       <c r="I15" t="n">
         <v>45.49340975401097</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K15" t="n">
-        <v>-5.73</v>
+        <v>-9.43</v>
       </c>
       <c r="L15" t="n">
-        <v>9.07</v>
+        <v>9.9</v>
       </c>
       <c r="M15" t="n">
         <v>1.23</v>
       </c>
       <c r="N15" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="O15" t="n">
         <v>-1.99</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42733</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>11.74</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>42811</v>
+        <v>42814</v>
       </c>
       <c r="H16" t="n">
-        <v>65.3</v>
+        <v>59</v>
       </c>
       <c r="I16" t="n">
         <v>61.40409317139493</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="K16" t="n">
-        <v>42.42</v>
+        <v>28.68</v>
       </c>
       <c r="L16" t="n">
         <v>3.27</v>
@@ -1353,7 +1544,7 @@
         <v>4.95</v>
       </c>
       <c r="N16" t="n">
-        <v>4.25</v>
+        <v>9.65</v>
       </c>
       <c r="O16" t="n">
         <v>3.5</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>35.77</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>42864</v>
+        <v>42865</v>
       </c>
       <c r="H17" t="n">
-        <v>52.55</v>
+        <v>54.8</v>
       </c>
       <c r="I17" t="n">
         <v>53.50434392795035</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K17" t="n">
-        <v>10.93</v>
+        <v>7.12</v>
       </c>
       <c r="L17" t="n">
         <v>26.44</v>
@@ -1419,7 +1622,19 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>42824</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1446,22 +1661,22 @@
         <v>13.24</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>42878</v>
+        <v>42879</v>
       </c>
       <c r="H18" t="n">
-        <v>51.05</v>
+        <v>47.6</v>
       </c>
       <c r="I18" t="n">
         <v>49.07897920398459</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K18" t="n">
-        <v>-6.84</v>
+        <v>-13.14</v>
       </c>
       <c r="L18" t="n">
-        <v>7.85</v>
+        <v>15.42</v>
       </c>
       <c r="M18" t="n">
         <v>1.14</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>42880</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>17</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>42914</v>
+        <v>42915</v>
       </c>
       <c r="H19" t="n">
-        <v>50.45</v>
+        <v>50.95</v>
       </c>
       <c r="I19" t="n">
         <v>50.72660771342701</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K19" t="n">
-        <v>-5.99</v>
+        <v>-7.04</v>
       </c>
       <c r="L19" t="n">
-        <v>7.67</v>
+        <v>8.4</v>
       </c>
       <c r="M19" t="n">
         <v>1.56</v>
@@ -1533,7 +1760,19 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>42880</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,22 +1799,22 @@
         <v>9.289999999999999</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>42983</v>
+        <v>42984</v>
       </c>
       <c r="H20" t="n">
-        <v>51.15</v>
+        <v>49.4</v>
       </c>
       <c r="I20" t="n">
         <v>50.99427247920175</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K20" t="n">
-        <v>0.39</v>
+        <v>-3.04</v>
       </c>
       <c r="L20" t="n">
-        <v>2.94</v>
+        <v>3.24</v>
       </c>
       <c r="M20" t="n">
         <v>5.54</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>42943</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>13.03</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43021</v>
+        <v>43024</v>
       </c>
       <c r="H21" t="n">
-        <v>47.65</v>
+        <v>50.2</v>
       </c>
       <c r="I21" t="n">
         <v>48.82091411112442</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K21" t="n">
-        <v>3.54</v>
+        <v>-1.62</v>
       </c>
       <c r="L21" t="n">
         <v>3.34</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>13.36</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43052</v>
+        <v>43053</v>
       </c>
       <c r="H22" t="n">
-        <v>56.4</v>
+        <v>55.85</v>
       </c>
       <c r="I22" t="n">
         <v>56.05597489441034</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K22" t="n">
-        <v>12.35</v>
+        <v>11.25</v>
       </c>
       <c r="L22" t="n">
         <v>4.98</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43034</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>17.13</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43097</v>
+        <v>43098</v>
       </c>
       <c r="H23" t="n">
-        <v>61.85</v>
+        <v>65.3</v>
       </c>
       <c r="I23" t="n">
         <v>62.241343394433</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K23" t="n">
-        <v>-10.74</v>
+        <v>-16.92</v>
       </c>
       <c r="L23" t="n">
-        <v>13.43</v>
+        <v>17.82</v>
       </c>
       <c r="M23" t="n">
         <v>1.77</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43069</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1788,22 +2075,22 @@
         <v>13.26</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43123</v>
+        <v>43124</v>
       </c>
       <c r="H24" t="n">
-        <v>60</v>
+        <v>56.7</v>
       </c>
       <c r="I24" t="n">
         <v>59.07126887234568</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K24" t="n">
-        <v>-8.119999999999999</v>
+        <v>-13.17</v>
       </c>
       <c r="L24" t="n">
-        <v>8.58</v>
+        <v>14.24</v>
       </c>
       <c r="M24" t="n">
         <v>4.93</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43125</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>17.82</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43245</v>
+        <v>43248</v>
       </c>
       <c r="H25" t="n">
-        <v>36.1</v>
+        <v>37.05</v>
       </c>
       <c r="I25" t="n">
         <v>36.18828071987512</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="K25" t="n">
-        <v>36.33</v>
+        <v>34.66</v>
       </c>
       <c r="L25" t="n">
         <v>5.47</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43125</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>5</v>
+      </c>
+      <c r="U25" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>13.95</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43284</v>
+        <v>43285</v>
       </c>
       <c r="H26" t="n">
-        <v>34.3</v>
+        <v>33.3</v>
       </c>
       <c r="I26" t="n">
         <v>33.45490382321805</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K26" t="n">
-        <v>-7.42</v>
+        <v>-10.12</v>
       </c>
       <c r="L26" t="n">
         <v>11.2</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>17.2</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43308</v>
+        <v>43311</v>
       </c>
       <c r="H27" t="n">
-        <v>34.05</v>
+        <v>35.25</v>
       </c>
       <c r="I27" t="n">
         <v>34.7178250156976</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K27" t="n">
-        <v>-2.25</v>
+        <v>-5.86</v>
       </c>
       <c r="L27" t="n">
         <v>11.11</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43307</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,22 +2351,22 @@
         <v>18.91</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43347</v>
+        <v>43348</v>
       </c>
       <c r="H28" t="n">
-        <v>29.85</v>
+        <v>28.95</v>
       </c>
       <c r="I28" t="n">
         <v>29.40592073638271</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K28" t="n">
-        <v>-15.32</v>
+        <v>-17.87</v>
       </c>
       <c r="L28" t="n">
-        <v>16.31</v>
+        <v>19.72</v>
       </c>
       <c r="M28" t="n">
         <v>3.55</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>15.87</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43406</v>
+        <v>43409</v>
       </c>
       <c r="H29" t="n">
-        <v>24.5</v>
+        <v>25.2</v>
       </c>
       <c r="I29" t="n">
         <v>24.7116571773039</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="K29" t="n">
-        <v>15.37</v>
+        <v>12.95</v>
       </c>
       <c r="L29" t="n">
         <v>4.66</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -2130,22 +2489,22 @@
         <v>15.1</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43433</v>
+        <v>43434</v>
       </c>
       <c r="H30" t="n">
-        <v>22.85</v>
+        <v>21.3</v>
       </c>
       <c r="I30" t="n">
         <v>22.16878236459441</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K30" t="n">
-        <v>-9.33</v>
+        <v>-15.48</v>
       </c>
       <c r="L30" t="n">
-        <v>13.29</v>
+        <v>15.87</v>
       </c>
       <c r="M30" t="n">
         <v>3</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>26.75</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43532</v>
+        <v>43535</v>
       </c>
       <c r="H31" t="n">
-        <v>19.65</v>
+        <v>20.65</v>
       </c>
       <c r="I31" t="n">
         <v>20.44025509372264</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="K31" t="n">
-        <v>7.75</v>
+        <v>3.05</v>
       </c>
       <c r="L31" t="n">
         <v>10.09</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43461</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>4</v>
+      </c>
+      <c r="U31" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="32">
@@ -2244,22 +2627,22 @@
         <v>14.27</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>43549</v>
+        <v>43550</v>
       </c>
       <c r="H32" t="n">
-        <v>18.25</v>
+        <v>17.9</v>
       </c>
       <c r="I32" t="n">
         <v>18.10802129273695</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K32" t="n">
-        <v>-11.62</v>
+        <v>-13.32</v>
       </c>
       <c r="L32" t="n">
-        <v>13.32</v>
+        <v>14.04</v>
       </c>
       <c r="M32" t="n">
         <v>0.26</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>17.38</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>43749</v>
+        <v>43752</v>
       </c>
       <c r="H33" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="I33" t="n">
         <v>6.293977789173606</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="K33" t="n">
-        <v>66.48</v>
+        <v>64.25</v>
       </c>
       <c r="L33" t="n">
         <v>14.25</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>133</v>
+        <v>134</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>8</v>
+      </c>
+      <c r="U33" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="34">
@@ -2358,28 +2765,28 @@
         <v>32.78</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>43761</v>
+        <v>43762</v>
       </c>
       <c r="H34" t="n">
-        <v>5.65</v>
+        <v>4.35</v>
       </c>
       <c r="I34" t="n">
         <v>4.690225980876786</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K34" t="n">
-        <v>-11.72</v>
+        <v>-32.03</v>
       </c>
       <c r="L34" t="n">
-        <v>13.28</v>
+        <v>35.94</v>
       </c>
       <c r="M34" t="n">
         <v>2.29</v>
       </c>
       <c r="N34" t="n">
-        <v>7.38</v>
+        <v>23.01</v>
       </c>
       <c r="O34" t="n">
         <v>6.67</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>43769</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2415,28 +2834,28 @@
         <v>59.25</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>43787</v>
+        <v>43788</v>
       </c>
       <c r="H35" t="n">
-        <v>4.45</v>
+        <v>6.05</v>
       </c>
       <c r="I35" t="n">
         <v>4.843388944389128</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K35" t="n">
-        <v>-2.3</v>
+        <v>-39.08</v>
       </c>
       <c r="L35" t="n">
-        <v>29.89</v>
+        <v>47.13</v>
       </c>
       <c r="M35" t="n">
-        <v>8.220000000000001</v>
+        <v>8.99</v>
       </c>
       <c r="N35" t="n">
-        <v>23.73</v>
+        <v>35.96</v>
       </c>
       <c r="O35" t="n">
         <v>-23.01</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>43769</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,28 +2903,28 @@
         <v>47.14</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>43846</v>
+        <v>43847</v>
       </c>
       <c r="H36" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="I36" t="n">
         <v>5.039839823921628</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.83</v>
+        <v>-25.62</v>
       </c>
       <c r="L36" t="n">
-        <v>19.83</v>
+        <v>39.67</v>
       </c>
       <c r="M36" t="n">
-        <v>5.8</v>
+        <v>10</v>
       </c>
       <c r="N36" t="n">
-        <v>12.41</v>
+        <v>25</v>
       </c>
       <c r="O36" t="n">
         <v>35.96</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>43797</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>42.31</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>43902</v>
+        <v>43903</v>
       </c>
       <c r="H37" t="n">
-        <v>4.2</v>
+        <v>5.6</v>
       </c>
       <c r="I37" t="n">
         <v>4.943128533126049</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K37" t="n">
-        <v>6.67</v>
+        <v>-24.44</v>
       </c>
       <c r="L37" t="n">
         <v>35.56</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2586,28 +3041,28 @@
         <v>57.25</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>43907</v>
+        <v>43908</v>
       </c>
       <c r="H38" t="n">
-        <v>4.85</v>
+        <v>3.15</v>
       </c>
       <c r="I38" t="n">
         <v>3.331923974947434</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K38" t="n">
-        <v>-13.39</v>
+        <v>-43.75</v>
       </c>
       <c r="L38" t="n">
-        <v>31.25</v>
+        <v>51.79</v>
       </c>
       <c r="M38" t="n">
         <v>4.76</v>
       </c>
       <c r="N38" t="n">
-        <v>14.91</v>
+        <v>35.05</v>
       </c>
       <c r="O38" t="n">
         <v>33.33</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>43916</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>147.23</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>43959</v>
+        <v>43962</v>
       </c>
       <c r="H39" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="I39" t="n">
         <v>4.490575533455585</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="K39" t="n">
-        <v>-33.33</v>
+        <v>-46.03</v>
       </c>
       <c r="L39" t="n">
         <v>80.95</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>43916</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>26.44</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44026</v>
+        <v>44027</v>
       </c>
       <c r="H40" t="n">
-        <v>9.35</v>
+        <v>8.65</v>
       </c>
       <c r="I40" t="n">
         <v>8.897385583646185</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K40" t="n">
-        <v>103.26</v>
+        <v>88.04000000000001</v>
       </c>
       <c r="L40" t="n">
         <v>8.699999999999999</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>43979</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>3</v>
+      </c>
+      <c r="U40" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -2757,28 +3248,28 @@
         <v>30.68</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44070</v>
+        <v>44071</v>
       </c>
       <c r="H41" t="n">
-        <v>8.85</v>
+        <v>10.1</v>
       </c>
       <c r="I41" t="n">
         <v>10.06208674706707</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K41" t="n">
-        <v>-2.31</v>
+        <v>-16.76</v>
       </c>
       <c r="L41" t="n">
-        <v>12.14</v>
+        <v>20.81</v>
       </c>
       <c r="M41" t="n">
         <v>5.62</v>
       </c>
       <c r="N41" t="n">
-        <v>13.38</v>
+        <v>14.12</v>
       </c>
       <c r="O41" t="n">
         <v>-7.49</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44042</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>3</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>21.35</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44109</v>
+        <v>44110</v>
       </c>
       <c r="H42" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I42" t="n">
         <v>8.847283722535984</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K42" t="n">
-        <v>-10.89</v>
+        <v>-12.87</v>
       </c>
       <c r="L42" t="n">
         <v>24.26</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,25 +3386,25 @@
         <v>29.19</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44154</v>
+        <v>44155</v>
       </c>
       <c r="H43" t="n">
-        <v>9.25</v>
+        <v>10.05</v>
       </c>
       <c r="I43" t="n">
         <v>9.596994142829832</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K43" t="n">
-        <v>-5.11</v>
+        <v>-14.2</v>
       </c>
       <c r="L43" t="n">
-        <v>13.64</v>
+        <v>15.34</v>
       </c>
       <c r="M43" t="n">
-        <v>2.87</v>
+        <v>3.24</v>
       </c>
       <c r="N43" t="n">
         <v>9.43</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>17.59</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44224</v>
+        <v>44225</v>
       </c>
       <c r="H44" t="n">
-        <v>11.75</v>
+        <v>11.2</v>
       </c>
       <c r="I44" t="n">
         <v>11.21599075662787</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K44" t="n">
-        <v>16.92</v>
+        <v>11.44</v>
       </c>
       <c r="L44" t="n">
         <v>11.44</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44161</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>4</v>
+      </c>
+      <c r="U44" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>23.97</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44349</v>
+        <v>44350</v>
       </c>
       <c r="H45" t="n">
-        <v>8.800000000000001</v>
+        <v>9.35</v>
       </c>
       <c r="I45" t="n">
         <v>9.019864816323793</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="K45" t="n">
-        <v>21.43</v>
+        <v>16.52</v>
       </c>
       <c r="L45" t="n">
         <v>16.52</v>
@@ -3015,7 +3554,19 @@
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>5</v>
+      </c>
+      <c r="U45" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>13.54</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44378</v>
+        <v>44379</v>
       </c>
       <c r="H46" t="n">
-        <v>9.050000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I46" t="n">
         <v>8.971852524127979</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K46" t="n">
-        <v>-3.21</v>
+        <v>-5.88</v>
       </c>
       <c r="L46" t="n">
         <v>9.09</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44371</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>22.47</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44445</v>
+        <v>44446</v>
       </c>
       <c r="H47" t="n">
-        <v>7.25</v>
+        <v>8.25</v>
       </c>
       <c r="I47" t="n">
         <v>7.587951041902234</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K47" t="n">
-        <v>17.61</v>
+        <v>6.25</v>
       </c>
       <c r="L47" t="n">
         <v>12.5</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44406</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>3</v>
+      </c>
+      <c r="U47" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -3156,28 +3731,28 @@
         <v>30.93</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44571</v>
+        <v>44572</v>
       </c>
       <c r="H48" t="n">
-        <v>14.85</v>
+        <v>11.8</v>
       </c>
       <c r="I48" t="n">
         <v>13.08027293357448</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K48" t="n">
-        <v>80</v>
+        <v>43.03</v>
       </c>
       <c r="L48" t="n">
         <v>13.33</v>
       </c>
       <c r="M48" t="n">
-        <v>3.13</v>
+        <v>9.76</v>
       </c>
       <c r="N48" t="n">
-        <v>6.87</v>
+        <v>20.54</v>
       </c>
       <c r="O48" t="n">
         <v>13.79</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>86</v>
+        <v>87</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>5</v>
+      </c>
+      <c r="U48" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>34.43</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>44658</v>
+        <v>44659</v>
       </c>
       <c r="H49" t="n">
-        <v>10.9</v>
+        <v>11.2</v>
       </c>
       <c r="I49" t="n">
         <v>11.10667416161452</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K49" t="n">
-        <v>7.63</v>
+        <v>5.08</v>
       </c>
       <c r="L49" t="n">
         <v>15.25</v>
@@ -3243,7 +3830,19 @@
         <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>4</v>
+      </c>
+      <c r="U49" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="50">
@@ -3270,28 +3869,28 @@
         <v>13.78</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>44677</v>
+        <v>44678</v>
       </c>
       <c r="H50" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="I50" t="n">
         <v>9.656270901877418</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K50" t="n">
-        <v>-10.71</v>
+        <v>-14.29</v>
       </c>
       <c r="L50" t="n">
-        <v>13.39</v>
+        <v>15.18</v>
       </c>
       <c r="M50" t="n">
         <v>1</v>
       </c>
       <c r="N50" t="n">
-        <v>3.12</v>
+        <v>4</v>
       </c>
       <c r="O50" t="n">
         <v>2.75</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>14.29</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>44774</v>
+        <v>44775</v>
       </c>
       <c r="H51" t="n">
-        <v>9.1</v>
+        <v>9.4</v>
       </c>
       <c r="I51" t="n">
         <v>9.239164557388806</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K51" t="n">
-        <v>5.21</v>
+        <v>2.08</v>
       </c>
       <c r="L51" t="n">
         <v>6.25</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>5</v>
+      </c>
+      <c r="U51" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="52">
@@ -3384,28 +4007,28 @@
         <v>9.93</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>44832</v>
+        <v>44833</v>
       </c>
       <c r="H52" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="I52" t="n">
         <v>8.653767219399281</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K52" t="n">
-        <v>-4.26</v>
+        <v>-9.57</v>
       </c>
       <c r="L52" t="n">
-        <v>9.57</v>
+        <v>10.64</v>
       </c>
       <c r="M52" t="n">
         <v>2.19</v>
       </c>
       <c r="N52" t="n">
-        <v>4.66</v>
+        <v>5.56</v>
       </c>
       <c r="O52" t="n">
         <v>3.3</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>17.72</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>44908</v>
+        <v>44909</v>
       </c>
       <c r="H53" t="n">
-        <v>7.9</v>
+        <v>8.65</v>
       </c>
       <c r="I53" t="n">
         <v>8.488547775192231</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K53" t="n">
-        <v>7.06</v>
+        <v>-1.76</v>
       </c>
       <c r="L53" t="n">
         <v>8.24</v>
@@ -3462,7 +4097,7 @@
         <v>3.51</v>
       </c>
       <c r="N53" t="n">
-        <v>3.53</v>
+        <v>9.49</v>
       </c>
       <c r="O53" t="n">
         <v>-5.56</v>
@@ -3471,7 +4106,19 @@
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>3</v>
+      </c>
+      <c r="U53" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -3498,28 +4145,28 @@
         <v>13.49</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>44932</v>
+        <v>44935</v>
       </c>
       <c r="H54" t="n">
-        <v>7.8</v>
+        <v>7.45</v>
       </c>
       <c r="I54" t="n">
         <v>7.569526302094293</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K54" t="n">
-        <v>-9.83</v>
+        <v>-13.87</v>
       </c>
       <c r="L54" t="n">
-        <v>12.14</v>
+        <v>15.03</v>
       </c>
       <c r="M54" t="n">
         <v>0.62</v>
       </c>
       <c r="N54" t="n">
-        <v>4.37</v>
+        <v>4.49</v>
       </c>
       <c r="O54" t="n">
         <v>9.49</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,28 +4214,28 @@
         <v>13.65</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>44960</v>
+        <v>44963</v>
       </c>
       <c r="H55" t="n">
-        <v>6.85</v>
+        <v>8.25</v>
       </c>
       <c r="I55" t="n">
         <v>7.518791210933384</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K55" t="n">
-        <v>8.050000000000001</v>
+        <v>-10.74</v>
       </c>
       <c r="L55" t="n">
-        <v>5.37</v>
+        <v>15.44</v>
       </c>
       <c r="M55" t="n">
-        <v>1.47</v>
+        <v>9.49</v>
       </c>
       <c r="N55" t="n">
-        <v>6.25</v>
+        <v>20.44</v>
       </c>
       <c r="O55" t="n">
         <v>-4.49</v>
@@ -3585,7 +4244,19 @@
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,22 +4283,22 @@
         <v>22.04</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>44999</v>
+        <v>45000</v>
       </c>
       <c r="H56" t="n">
-        <v>6.55</v>
+        <v>6.4</v>
       </c>
       <c r="I56" t="n">
         <v>6.494013692111491</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K56" t="n">
-        <v>-20.61</v>
+        <v>-22.42</v>
       </c>
       <c r="L56" t="n">
-        <v>21.21</v>
+        <v>22.42</v>
       </c>
       <c r="M56" t="n">
         <v>1.42</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,22 +4352,22 @@
         <v>13.7</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45042</v>
+        <v>45043</v>
       </c>
       <c r="H57" t="n">
-        <v>6.55</v>
+        <v>6.9</v>
       </c>
       <c r="I57" t="n">
         <v>6.59630262181787</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K57" t="n">
-        <v>-2.34</v>
+        <v>-7.81</v>
       </c>
       <c r="L57" t="n">
-        <v>6.25</v>
+        <v>10.16</v>
       </c>
       <c r="M57" t="n">
         <v>1.65</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>13.31</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45322</v>
+        <v>45323</v>
       </c>
       <c r="H58" t="n">
-        <v>14.35</v>
+        <v>14.15</v>
       </c>
       <c r="I58" t="n">
         <v>14.16360878279534</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="K58" t="n">
-        <v>107.97</v>
+        <v>105.07</v>
       </c>
       <c r="L58" t="n">
         <v>5.07</v>
@@ -3756,7 +4451,19 @@
         <v>1</v>
       </c>
       <c r="Q58" t="n">
-        <v>191</v>
+        <v>192</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>10</v>
+      </c>
+      <c r="U58" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>15.7</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="H59" t="n">
-        <v>15.35</v>
+        <v>16.3</v>
       </c>
       <c r="I59" t="n">
         <v>16.01768457820135</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K59" t="n">
-        <v>-8.48</v>
+        <v>-15.19</v>
       </c>
       <c r="L59" t="n">
         <v>17.31</v>
@@ -3804,7 +4511,7 @@
         <v>1.75</v>
       </c>
       <c r="N59" t="n">
-        <v>5.78</v>
+        <v>6.19</v>
       </c>
       <c r="O59" t="n">
         <v>-1.39</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S59" t="b">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3840,28 +4559,28 @@
         <v>19.93</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="H60" t="n">
-        <v>15.85</v>
+        <v>13.65</v>
       </c>
       <c r="I60" t="n">
         <v>14.51447687082135</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K60" t="n">
-        <v>-2.76</v>
+        <v>-16.26</v>
       </c>
       <c r="L60" t="n">
-        <v>7.67</v>
+        <v>17.18</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="N60" t="n">
-        <v>5.93</v>
+        <v>13.88</v>
       </c>
       <c r="O60" t="n">
         <v>6.19</v>
@@ -3870,7 +4589,19 @@
         <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>35.43</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45435</v>
+        <v>45436</v>
       </c>
       <c r="H61" t="n">
-        <v>14.05</v>
+        <v>15.1</v>
       </c>
       <c r="I61" t="n">
         <v>14.62457676148982</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K61" t="n">
-        <v>-2.93</v>
+        <v>-10.62</v>
       </c>
       <c r="L61" t="n">
         <v>17.58</v>
@@ -3927,7 +4658,19 @@
         <v>1</v>
       </c>
       <c r="Q61" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>4</v>
+      </c>
+      <c r="U61" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="62">
@@ -3954,28 +4697,28 @@
         <v>14.42</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45446</v>
+        <v>45447</v>
       </c>
       <c r="H62" t="n">
-        <v>16</v>
+        <v>13.2</v>
       </c>
       <c r="I62" t="n">
         <v>13.91425496405236</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K62" t="n">
-        <v>5.96</v>
+        <v>-12.58</v>
       </c>
       <c r="L62" t="n">
-        <v>5.96</v>
+        <v>20.2</v>
       </c>
       <c r="M62" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.88</v>
       </c>
       <c r="N62" t="n">
-        <v>3.32</v>
+        <v>17.5</v>
       </c>
       <c r="O62" t="n">
         <v>7.47</v>
@@ -3984,7 +4727,19 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>28.48</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45463</v>
+        <v>45464</v>
       </c>
       <c r="H63" t="n">
-        <v>16.53</v>
+        <v>17.14</v>
       </c>
       <c r="I63" t="n">
         <v>16.95967053235287</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K63" t="n">
-        <v>-25.23</v>
+        <v>-29.85</v>
       </c>
       <c r="L63" t="n">
         <v>31.74</v>
@@ -4041,7 +4796,19 @@
         <v>1</v>
       </c>
       <c r="Q63" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S63" t="b">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>16.04</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45491</v>
+        <v>45492</v>
       </c>
       <c r="H64" t="n">
-        <v>16.27</v>
+        <v>15.87</v>
       </c>
       <c r="I64" t="n">
         <v>15.9519869047312</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K64" t="n">
-        <v>-5.08</v>
+        <v>-7.41</v>
       </c>
       <c r="L64" t="n">
         <v>7.93</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>15.99</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45622</v>
+        <v>45623</v>
       </c>
       <c r="H65" t="n">
-        <v>7.52</v>
+        <v>8.34</v>
       </c>
       <c r="I65" t="n">
         <v>7.835285590433241</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K65" t="n">
-        <v>52.61</v>
+        <v>47.45</v>
       </c>
       <c r="L65" t="n">
         <v>4.28</v>
@@ -4146,7 +4925,7 @@
         <v>9.9</v>
       </c>
       <c r="N65" t="n">
-        <v>7.89</v>
+        <v>10.9</v>
       </c>
       <c r="O65" t="n">
         <v>-2.46</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>89</v>
+        <v>90</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>5</v>
+      </c>
+      <c r="U65" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>22.6</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45699</v>
+        <v>45700</v>
       </c>
       <c r="H66" t="n">
-        <v>8.82</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="I66" t="n">
         <v>8.624096198356789</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K66" t="n">
-        <v>5.76</v>
+        <v>0.6</v>
       </c>
       <c r="L66" t="n">
         <v>11.99</v>
@@ -4212,7 +5003,19 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>4</v>
+      </c>
+      <c r="U66" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="67">
@@ -4239,28 +5042,28 @@
         <v>18.85</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>45744</v>
+        <v>45748</v>
       </c>
       <c r="H67" t="n">
-        <v>6.8</v>
+        <v>8.1</v>
       </c>
       <c r="I67" t="n">
         <v>8.018555044599465</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="K67" t="n">
-        <v>18.95</v>
+        <v>3.46</v>
       </c>
       <c r="L67" t="n">
         <v>7.15</v>
       </c>
       <c r="M67" t="n">
-        <v>2.11</v>
+        <v>10</v>
       </c>
       <c r="N67" t="n">
-        <v>5.79</v>
+        <v>19.12</v>
       </c>
       <c r="O67" t="n">
         <v>-4.88</v>
@@ -4269,7 +5072,19 @@
         <v>1</v>
       </c>
       <c r="Q67" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>3</v>
+      </c>
+      <c r="U67" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="68">
@@ -4296,22 +5111,22 @@
         <v>19.38</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>45784</v>
+        <v>45785</v>
       </c>
       <c r="H68" t="n">
-        <v>6.92</v>
+        <v>6.69</v>
       </c>
       <c r="I68" t="n">
         <v>6.865220706430042</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K68" t="n">
-        <v>-14.57</v>
+        <v>-17.41</v>
       </c>
       <c r="L68" t="n">
-        <v>16.67</v>
+        <v>17.9</v>
       </c>
       <c r="M68" t="n">
         <v>9.359999999999999</v>
@@ -4326,7 +5141,19 @@
         <v>1</v>
       </c>
       <c r="Q68" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>17.15</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>45833</v>
+        <v>45834</v>
       </c>
       <c r="H69" t="n">
-        <v>7.13</v>
+        <v>7.24</v>
       </c>
       <c r="I69" t="n">
         <v>7.225964968788255</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K69" t="n">
-        <v>-6.58</v>
+        <v>-8.220000000000001</v>
       </c>
       <c r="L69" t="n">
         <v>12.86</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4410,22 +5249,22 @@
         <v>12.23</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>45867</v>
+        <v>45868</v>
       </c>
       <c r="H70" t="n">
-        <v>7.19</v>
+        <v>7</v>
       </c>
       <c r="I70" t="n">
         <v>7.045819512943435</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K70" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-3.31</v>
       </c>
       <c r="L70" t="n">
-        <v>2.07</v>
+        <v>3.59</v>
       </c>
       <c r="M70" t="n">
         <v>0.82</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S70" t="b">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>1</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -4467,28 +5318,28 @@
         <v>11.79</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>45890</v>
+        <v>45891</v>
       </c>
       <c r="H71" t="n">
-        <v>6.55</v>
+        <v>7.07</v>
       </c>
       <c r="I71" t="n">
         <v>6.940766940698111</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K71" t="n">
-        <v>6.43</v>
+        <v>-1</v>
       </c>
       <c r="L71" t="n">
-        <v>3.43</v>
+        <v>4.43</v>
       </c>
       <c r="M71" t="n">
         <v>2.58</v>
       </c>
       <c r="N71" t="n">
-        <v>5.04</v>
+        <v>7.94</v>
       </c>
       <c r="O71" t="n">
         <v>-2.64</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>2</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -4524,19 +5387,19 @@
         <v>15.09</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="H72" t="n">
-        <v>12.06</v>
+        <v>10.76</v>
       </c>
       <c r="I72" t="n">
         <v>10.82151658456502</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K72" t="n">
-        <v>70.58</v>
+        <v>52.19</v>
       </c>
       <c r="L72" t="n">
         <v>8.630000000000001</v>
@@ -4545,7 +5408,7 @@
         <v>4.05</v>
       </c>
       <c r="N72" t="n">
-        <v>9.32</v>
+        <v>10.78</v>
       </c>
       <c r="O72" t="n">
         <v>7.94</v>
@@ -4554,7 +5417,19 @@
         <v>1</v>
       </c>
       <c r="Q72" t="n">
-        <v>88</v>
+        <v>89</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>6</v>
+      </c>
+      <c r="U72" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="73">
@@ -4581,19 +5456,19 @@
         <v>24.58</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="H73" t="n">
-        <v>10.81</v>
+        <v>11.41</v>
       </c>
       <c r="I73" t="n">
         <v>11.30335191816466</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K73" t="n">
-        <v>-0.46</v>
+        <v>-6.04</v>
       </c>
       <c r="L73" t="n">
         <v>18.96</v>
@@ -4611,7 +5486,19 @@
         <v>1</v>
       </c>
       <c r="Q73" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>2</v>
+      </c>
+      <c r="U73" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -4638,28 +5525,28 @@
         <v>18.11</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46083</v>
+        <v>46085</v>
       </c>
       <c r="H74" t="n">
-        <v>10.29</v>
+        <v>9.99</v>
       </c>
       <c r="I74" t="n">
         <v>10.28318197169603</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K74" t="n">
-        <v>-9.82</v>
+        <v>-12.45</v>
       </c>
       <c r="L74" t="n">
-        <v>11.48</v>
+        <v>13.67</v>
       </c>
       <c r="M74" t="n">
         <v>3.21</v>
       </c>
       <c r="N74" t="n">
-        <v>2.83</v>
+        <v>2.92</v>
       </c>
       <c r="O74" t="n">
         <v>5.55</v>
@@ -4668,7 +5555,19 @@
         <v>1</v>
       </c>
       <c r="Q74" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S74" t="b">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>2</v>
+      </c>
+      <c r="U74" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -4695,19 +5594,19 @@
         <v>12.53</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="H75" t="n">
-        <v>9.52</v>
+        <v>9.69</v>
       </c>
       <c r="I75" t="n">
         <v>9.634026262837827</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="K75" t="n">
-        <v>4.7</v>
+        <v>3</v>
       </c>
       <c r="L75" t="n">
         <v>3.9</v>
@@ -4725,7 +5624,19 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>2</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -4752,19 +5663,19 @@
         <v>9.43</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="H76" t="n">
-        <v>13.74</v>
+        <v>13.51</v>
       </c>
       <c r="I76" t="n">
         <v>13.62366773252111</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="K76" t="n">
-        <v>41.8</v>
+        <v>39.42</v>
       </c>
       <c r="L76" t="n">
         <v>1.34</v>
@@ -4782,7 +5693,19 @@
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S76" t="b">
+        <v>1</v>
+      </c>
+      <c r="T76" t="n">
+        <v>4</v>
+      </c>
+      <c r="U76" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="77">
@@ -4809,22 +5732,22 @@
         <v>9.59</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="H77" t="n">
-        <v>13.51</v>
+        <v>14.11</v>
       </c>
       <c r="I77" t="n">
         <v>13.69633993003228</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K77" t="n">
-        <v>0</v>
+        <v>-4.44</v>
       </c>
       <c r="L77" t="n">
-        <v>2.74</v>
+        <v>5.03</v>
       </c>
       <c r="M77" t="n">
         <v>1.7</v>
@@ -4839,7 +5762,19 @@
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S77" t="b">
+        <v>1</v>
+      </c>
+      <c r="T77" t="n">
+        <v>2</v>
+      </c>
+      <c r="U77" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -4866,19 +5801,19 @@
         <v>10.95</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="H78" t="n">
-        <v>14.22</v>
+        <v>13.92</v>
       </c>
       <c r="I78" t="n">
         <v>13.95452410925055</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K78" t="n">
-        <v>0.78</v>
+        <v>-1.35</v>
       </c>
       <c r="L78" t="n">
         <v>4.39</v>
@@ -4896,7 +5831,19 @@
         <v>1</v>
       </c>
       <c r="Q78" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R78" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S78" t="b">
+        <v>1</v>
+      </c>
+      <c r="T78" t="n">
+        <v>2</v>
+      </c>
+      <c r="U78" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -4947,6 +5894,14 @@
       <c r="Q79" t="n">
         <v>27</v>
       </c>
+      <c r="R79" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S79" t="b">
+        <v>1</v>
+      </c>
+      <c r="T79" t="inlineStr"/>
+      <c r="U79" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9905,7 +10860,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>53.9</v>
+        <v>55.4</v>
       </c>
     </row>
     <row r="6">
@@ -9915,7 +10870,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7">
@@ -9925,7 +10880,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="8">
@@ -9935,7 +10890,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -9945,7 +10900,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10">
@@ -9955,7 +10910,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>115</v>
+        <v>116.8</v>
       </c>
     </row>
     <row r="11">
@@ -9995,7 +10950,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7.04</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="15">
@@ -10005,7 +10960,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7.81</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="16">
@@ -10015,7 +10970,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6.24</v>
+        <v>-0.95</v>
       </c>
     </row>
     <row r="17">
@@ -10025,7 +10980,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>107.97</v>
+        <v>105.07</v>
       </c>
     </row>
     <row r="18">
@@ -10035,7 +10990,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>48.1</v>
+        <v>36.4</v>
       </c>
     </row>
     <row r="19">
@@ -10045,7 +11000,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>11.72</v>
+        <v>14.12</v>
       </c>
     </row>
     <row r="20">
@@ -10055,7 +11010,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>9.07</v>
+        <v>11.44</v>
       </c>
     </row>
     <row r="21">
@@ -10075,7 +11030,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="23">
@@ -10085,7 +11040,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
     </row>
     <row r="24">
@@ -10095,7 +11050,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3.39</v>
+        <v>3.88</v>
       </c>
     </row>
     <row r="25">
@@ -10115,7 +11070,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>7.84</v>
+        <v>9.859999999999999</v>
       </c>
     </row>
     <row r="27">
@@ -10135,7 +11090,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
     </row>
     <row r="29">
